--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487464_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487464_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1176</v>
+        <v>11.026</v>
       </c>
       <c r="E2" t="n">
-        <v>7.747</v>
+        <v>8.3345</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3706</v>
+        <v>2.6914</v>
       </c>
       <c r="G2" t="n">
         <v>9.2103</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1122</v>
+        <v>-1.2039</v>
       </c>
       <c r="T2" t="n">
-        <v>0.17</v>
+        <v>0.7575</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.2822</v>
+        <v>-1.9614</v>
       </c>
       <c r="V2" t="n">
         <v>2.8237</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6491</v>
+        <v>8.805199999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9484</v>
+        <v>6.5163</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7008</v>
+        <v>2.2888</v>
       </c>
       <c r="G3" t="n">
         <v>10.0503</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.1478</v>
+        <v>-1.9917</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3133</v>
+        <v>0.2547</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.8345</v>
+        <v>-2.2464</v>
       </c>
       <c r="V3" t="n">
         <v>0.5507</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1299</v>
+        <v>4.9938</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7589</v>
+        <v>4.3268</v>
       </c>
       <c r="F4" t="n">
-        <v>4.371</v>
+        <v>0.667</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8859</v>
+        <v>5.053</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0331</v>
+        <v>1.9555</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8528</v>
+        <v>3.0975</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.7835</v>
+        <v>3.6501</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.1068</v>
+        <v>0.4525</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3233</v>
+        <v>3.1976</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8976</v>
+        <v>1.4029</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0737</v>
+        <v>1.503</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1761</v>
+        <v>-0.1001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9585</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8971</v>
+        <v>-0.7043</v>
       </c>
       <c r="T4" t="n">
-        <v>4.3822</v>
+        <v>0.4393</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5149</v>
+        <v>-1.1436</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1602</v>
+        <v>0.0576</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1602</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6867</v>
+        <v>2.2398</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2869</v>
+        <v>-0.9283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3997</v>
+        <v>3.1681</v>
       </c>
       <c r="G5" t="n">
-        <v>5.053</v>
+        <v>-0.8859</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9555</v>
+        <v>-0.0331</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0975</v>
+        <v>-0.8528</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6501</v>
+        <v>-2.7835</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4525</v>
+        <v>-3.1068</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1976</v>
+        <v>0.3233</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4029</v>
+        <v>1.8976</v>
       </c>
       <c r="N5" t="n">
-        <v>1.503</v>
+        <v>3.0737</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1001</v>
+        <v>-1.1761</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>1.9585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0114</v>
+        <v>1.007</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6005</v>
+        <v>1.695</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4109</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0576</v>
+        <v>0.1602</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0.1602</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3595</v>
+        <v>0.3341</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1458</v>
+        <v>-1.9841</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5053</v>
+        <v>2.3182</v>
       </c>
       <c r="G6" t="n">
         <v>1.2751</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0734</v>
+        <v>-1.0988</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0723</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0011</v>
+        <v>-1.1882</v>
       </c>
       <c r="V6" t="n">
         <v>0.9412</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7992</v>
+        <v>-0.5352</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0171</v>
+        <v>0.2469</v>
       </c>
       <c r="F7" t="n">
         <v>-0.7821</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.1694</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1188</v>
+        <v>0.1453</v>
       </c>
       <c r="U7" t="n">
         <v>0.0241</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.794</v>
+        <v>-3.5369</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6323</v>
+        <v>-0.6158</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1617</v>
+        <v>-2.9211</v>
       </c>
       <c r="G8" t="n">
         <v>1.2826</v>
@@ -1078,13 +1078,13 @@
         <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8012</v>
+        <v>-0.5442</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2664</v>
+        <v>0.2829</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0676</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-2.7086</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.9294</v>
+        <v>-6.7185</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.026999999999999</v>
+        <v>-7.7893</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0976</v>
+        <v>1.0709</v>
       </c>
       <c r="G9" t="n">
         <v>-5.0576</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.4651</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2711</v>
+        <v>0.5087</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9738</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>15.4202</v>
+        <v>16.6083</v>
       </c>
       <c r="E10" t="n">
-        <v>6.918999999999999</v>
+        <v>8.106999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>8.501200000000003</v>
+        <v>8.501200000000001</v>
       </c>
       <c r="G10" t="n">
         <v>20.8315</v>
@@ -1234,10 +1234,10 @@
         <v>10.7716</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.0195</v>
+        <v>-4.8316</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9848</v>
+        <v>4.172800000000001</v>
       </c>
       <c r="U10" t="n">
         <v>-9.0044</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9709</v>
+        <v>2.2624</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1995</v>
+        <v>3.6357</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2286</v>
+        <v>-1.3732</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2336</v>
+        <v>0.3394</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6704</v>
+        <v>-3.5145</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.904</v>
+        <v>3.8539</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4185</v>
+        <v>2.0571</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2569</v>
+        <v>-3.3874</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1617</v>
+        <v>5.4445</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6521</v>
+        <v>-1.7177</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4135</v>
+        <v>-0.1271</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0656</v>
+        <v>-1.5906</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8182</v>
+        <v>1.4411</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7015</v>
+        <v>1.7744</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8833</v>
+        <v>-0.3333</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.397</v>
+        <v>-1.2807</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6724</v>
+        <v>-1.2807</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8381</v>
+        <v>0.6123</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0216</v>
+        <v>1.3808</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1835</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3394</v>
+        <v>-0.2336</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.5145</v>
+        <v>0.6704</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8539</v>
+        <v>-0.904</v>
       </c>
       <c r="J12" t="n">
-        <v>2.0571</v>
+        <v>0.4185</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.3874</v>
+        <v>0.2569</v>
       </c>
       <c r="L12" t="n">
-        <v>5.4445</v>
+        <v>0.1617</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7177</v>
+        <v>-0.6521</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1271</v>
+        <v>0.4135</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5906</v>
+        <v>-1.0656</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0168</v>
+        <v>0.4595</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1604</v>
+        <v>0.8828</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1436</v>
+        <v>-0.4233</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2807</v>
+        <v>-0.397</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2807</v>
+        <v>-0.6724</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3629</v>
+        <v>-0.0264</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2142</v>
+        <v>0.5212</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5476</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1939</v>
@@ -1468,13 +1468,13 @@
         <v>0.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4392</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5393</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1001</v>
+        <v>-0.0706</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9523</v>
+        <v>-0.3964</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5148</v>
+        <v>-1.2078</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5624</v>
+        <v>0.8114</v>
       </c>
       <c r="G14" t="n">
         <v>-3.6235</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6765</v>
+        <v>1.2324</v>
       </c>
       <c r="T14" t="n">
-        <v>0.841</v>
+        <v>1.148</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1646</v>
+        <v>0.0844</v>
       </c>
       <c r="V14" t="n">
         <v>0.8196</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8033</v>
+        <v>-1.1411</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.1456</v>
+        <v>-0.8408</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3423</v>
+        <v>-0.3002</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.0662</v>
+        <v>-3.0465</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.9301</v>
+        <v>0.2835</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1361</v>
+        <v>-3.33</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.3567</v>
+        <v>-1.2548</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.478</v>
+        <v>0.6158</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1212</v>
+        <v>-1.8706</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2905</v>
+        <v>-1.7917</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5479000000000001</v>
+        <v>-0.3323</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2573</v>
+        <v>-1.4594</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1626</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8942</v>
+        <v>1.1339</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2684</v>
+        <v>-0.1495</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2754</v>
+        <v>1.3127</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2754</v>
+        <v>1.4344</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0192</v>
+        <v>-1.5213</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.874</v>
+        <v>-2.0553</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8547</v>
+        <v>0.534</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0242</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3978</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0194</v>
+        <v>0.7993</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4172</v>
+        <v>0.0965</v>
       </c>
       <c r="V16" t="n">
         <v>0.3905</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3396</v>
+        <v>-2.1349</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9022</v>
+        <v>-0.6975</v>
       </c>
       <c r="F17" t="n">
         <v>-1.4374</v>
@@ -1780,10 +1780,10 @@
         <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.297</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.22</v>
+        <v>-0.0153</v>
       </c>
       <c r="U17" t="n">
         <v>-0.077</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.009</v>
+        <v>-2.5979</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4415</v>
+        <v>-1.5439</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5675</v>
+        <v>-1.054</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0086</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8253</v>
+        <v>-0.4142</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0129</v>
+        <v>-0.1153</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8124</v>
+        <v>-0.2989</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2758</v>
+        <v>-3.5448</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3756</v>
+        <v>-4.783</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9002</v>
+        <v>1.2382</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9527</v>
+        <v>-4.0662</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.942</v>
+        <v>-3.9301</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0107</v>
+        <v>-0.1361</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.484</v>
+        <v>-4.3567</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.5389</v>
+        <v>-4.478</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0549</v>
+        <v>0.1212</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4687</v>
+        <v>0.2905</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4031</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0656</v>
+        <v>-0.2573</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7834</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9725</v>
+        <v>1.4211</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8283</v>
+        <v>1.2568</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1442</v>
+        <v>0.1642</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5122</v>
+        <v>0.2754</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4344</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.9466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.467</v>
+        <v>-4.8855</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6829</v>
+        <v>-2.9107</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7842</v>
+        <v>-1.9748</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0465</v>
+        <v>-4.9527</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2835</v>
+        <v>-3.942</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.33</v>
+        <v>-1.0107</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2548</v>
+        <v>-3.484</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6158</v>
+        <v>-3.5389</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8706</v>
+        <v>0.0549</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7917</v>
+        <v>-1.4687</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3323</v>
+        <v>-0.4031</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4594</v>
+        <v>-1.0656</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3416</v>
+        <v>1.3629</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7081</v>
+        <v>1.2933</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6335</v>
+        <v>0.0696</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3127</v>
+        <v>-0.5122</v>
       </c>
       <c r="W20" t="n">
         <v>1.4344</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1217</v>
+        <v>-1.9466</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-15.4201</v>
+        <v>-13.3736</v>
       </c>
       <c r="E21" t="n">
         <v>-8.501300000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.9191</v>
+        <v>-4.8722</v>
       </c>
       <c r="G21" t="n">
         <v>-20.8316</v>
@@ -2080,10 +2080,10 @@
         <v>-0.2917999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-7.953200000000001</v>
+        <v>-7.9532</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.0001000000000001555</v>
+        <v>-9.999999999987796e-05</v>
       </c>
       <c r="Q21" t="n">
         <v>-10.7715</v>
@@ -2092,22 +2092,22 @@
         <v>10.7715</v>
       </c>
       <c r="S21" t="n">
-        <v>6.0197</v>
+        <v>8.0663</v>
       </c>
       <c r="T21" t="n">
-        <v>9.004300000000001</v>
+        <v>9.004200000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.9847</v>
+        <v>-0.9378999999999998</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6082999999999998</v>
       </c>
       <c r="W21" t="n">
-        <v>5.852799999999999</v>
+        <v>5.8528</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.461099999999999</v>
+        <v>-6.4611</v>
       </c>
     </row>
   </sheetData>
